--- a/astro-site/public/dl/hotel-checklist-templates/13-hotel-preventive-maintenance-checklists.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/13-hotel-preventive-maintenance-checklists.xlsx
@@ -672,7 +672,7 @@
     <row r="15">
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>▸ The "Frequency" column already gives the legal or recommended frequency of each check; note the part number and the date of the next one in "Notes".</t>
+          <t>▸ The "Frequency" column already gives the legal or recommended frequency of each check; note the report number and the date of the next one in "Notes".</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Optional third-party food safety audit or ATP swab testing to verify your cleaning (many brands require an annual audit)</t>
+          <t>Optional third-party food safety audit or ATP swab testing to verify your cleaning (many brands require one or two a year)</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Renew food handler cards and allergen training for all F&amp;B staff, banquet extras included, and check a certified food protection manager is on the F&amp;B management team (FDA Food Code 2-102.12; card rules vary by state)</t>
+          <t>Check food handler cards are current for all F&amp;B staff, banquet extras included (renew them when your state requires), refresh allergen training, and check a certified food protection manager is on the F&amp;B management team (FDA Food Code 2-102.12; card rules vary by state)</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Drain, deep-clean and inspect pool and spa shells, filters and showers; check every drain cover is VGB-compliant and within its service life (15 U.S.C. 8003)</t>
+          <t>Drain, deep-clean and inspect pool and spa shells, filters and showers; check every drain cover is VGB-compliant and within its service life (15 U.S.C. 8003); the hot tub itself is drained, scrubbed and refilled far more often (MAHC 2024 §5.12.1.2)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Evacuation drill with every shift, as often as your local fire code requires, and review of the emergency action plan</t>
+          <t>Evacuation drill on every shift, with the emergency action plan reviewed: model fire codes require hotels to drill staff quarterly on each shift (IFC Table 405.2, Group R-1); your local fire code governs</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
@@ -2167,7 +2167,7 @@
       <c r="E27" s="12" t="n"/>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="G27" s="13" t="n"/>
